--- a/public/data/sample-stunting-periode-2.xlsx
+++ b/public/data/sample-stunting-periode-2.xlsx
@@ -398,6 +398,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H12"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,7 +432,7 @@
         <v>Desa/Kelurahan</v>
       </c>
       <c r="H1" t="str">
-        <v>Status Stunting</v>
+        <v>Status Gizi</v>
       </c>
     </row>
     <row r="2">
@@ -482,13 +492,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>3301020301230003</v>
+        <v>3301020301210003</v>
       </c>
       <c r="C4" t="str">
-        <v>Budi Santoso</v>
+        <v>Budi Santoso (Outlier Usia)</v>
       </c>
       <c r="D4" t="str">
-        <v>2023-01-03</v>
+        <v>2021-04-10</v>
       </c>
       <c r="E4" t="str">
         <v>L</v>
@@ -586,7 +596,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>3301066103230012</v>
+        <v>3301066103230013</v>
       </c>
       <c r="C8" t="str">
         <v>Zahra Aulia</v>
@@ -612,7 +622,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>3301071408230013</v>
+        <v>3301071408230014</v>
       </c>
       <c r="C9" t="str">
         <v>Ilham Hidayat</v>
@@ -638,7 +648,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>3301075609230014</v>
+        <v>3301075609230015</v>
       </c>
       <c r="C10" t="str">
         <v>Putri Maharani</v>
@@ -664,7 +674,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>3301082201240015</v>
+        <v>3301082201240016</v>
       </c>
       <c r="C11" t="str">
         <v>Kenzo Alfarizi</v>
@@ -690,7 +700,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>3301086504230016</v>
+        <v>3301086504230017</v>
       </c>
       <c r="C12" t="str">
         <v>Alya Shabila</v>
